--- a/exports/MCX_full_report.xlsx
+++ b/exports/MCX_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>4.17</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I2" t="n">
         <v>310.82450269773</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.48</v>
+        <v>-3.73</v>
       </c>
       <c r="L2" t="n">
-        <v>3.73</v>
+        <v>4.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31</v>
+        <v>0.96</v>
       </c>
       <c r="N2" t="n">
         <v>2.79</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.03</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="I3" t="n">
         <v>315.2773746731248</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.32</v>
+        <v>-3.23</v>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>3.87</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="N3" t="n">
         <v>3.73</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.63</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44595.38541666666</v>
+        <v>44595.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I4" t="n">
         <v>295.5866130292666</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.88</v>
+        <v>-8.44</v>
       </c>
       <c r="L4" t="n">
-        <v>7.19</v>
+        <v>8.75</v>
       </c>
       <c r="M4" t="n">
         <v>0.32</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.48</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="I5" t="n">
         <v>261.7447619934609</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>13.31</v>
+        <v>6.48</v>
       </c>
       <c r="L5" t="n">
         <v>2.05</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.19</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.38541666666</v>
+        <v>44664.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I6" t="n">
         <v>280.7579502239387</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="L6" t="n">
         <v>11.31</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.39</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="I7" t="n">
         <v>284.4933658829763</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>1.07</v>
+        <v>-2.14</v>
       </c>
       <c r="L7" t="n">
-        <v>1.07</v>
+        <v>2.86</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.37</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I8" t="n">
         <v>269.5675026441792</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.24</v>
+        <v>-6.29</v>
       </c>
       <c r="L8" t="n">
-        <v>5.59</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
         <v>0.35</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44698.55208333334</v>
+        <v>44699.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="I9" t="n">
         <v>252.7319145922653</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9.33</v>
+        <v>4.48</v>
       </c>
       <c r="L9" t="n">
         <v>2.61</v>
@@ -954,7 +1061,7 @@
         <v>5.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.97</v>
+        <v>5.76</v>
       </c>
       <c r="O9" t="n">
         <v>-3.69</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.52</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I10" t="n">
         <v>252.5884356813145</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>0.78</v>
+        <v>-2.73</v>
       </c>
       <c r="L10" t="n">
         <v>5.47</v>
@@ -1011,7 +1130,7 @@
         <v>3.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>3.88</v>
       </c>
       <c r="O10" t="n">
         <v>5.76</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44736.38541666666</v>
+        <v>44736.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I11" t="n">
         <v>253.4895888976481</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.61</v>
+        <v>-2.01</v>
       </c>
       <c r="L11" t="n">
         <v>4.82</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.49</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="I12" t="n">
         <v>272.8167528327415</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>9.449999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="L12" t="n">
         <v>1.97</v>
@@ -1125,7 +1268,7 @@
         <v>0.79</v>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>5.04</v>
       </c>
       <c r="O12" t="n">
         <v>2.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.44</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44791.38541666666</v>
+        <v>44791.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I13" t="n">
         <v>266.4461974225187</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="L13" t="n">
         <v>5.64</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>4.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I14" t="n">
         <v>255.8608548355395</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.46</v>
+        <v>-5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>5.58</v>
       </c>
       <c r="M14" t="n">
         <v>-0</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I15" t="n">
         <v>251.1792778283764</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>1.96</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
         <v>3.14</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.19</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="I16" t="n">
         <v>319.4817649981161</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>78</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>27.17</v>
+        <v>25.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.18</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.67</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44938.55208333334</v>
+        <v>44939.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="I17" t="n">
         <v>303.6838654705043</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>4.72</v>
+        <v>0.31</v>
       </c>
       <c r="L17" t="n">
         <v>1.57</v>
@@ -1410,7 +1613,7 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>2.06</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
         <v>-3.64</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.55</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I18" t="n">
         <v>306.6708635264801</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.21</v>
+        <v>-5.36</v>
       </c>
       <c r="L18" t="n">
-        <v>4.42</v>
+        <v>5.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>3.23</v>
       </c>
       <c r="O18" t="n">
         <v>5.28</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>7.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I19" t="n">
         <v>288.2263672260107</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="L19" t="n">
         <v>3.33</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>2.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.44</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45034.38541666666</v>
+        <v>45034.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I20" t="n">
         <v>291.8200960460578</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>1.04</v>
+        <v>0.35</v>
       </c>
       <c r="L20" t="n">
         <v>1.38</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="I21" t="n">
         <v>279.4312808984141</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>5.86</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>2.76</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="I22" t="n">
         <v>305.5953289933497</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>16.79</v>
+        <v>7.14</v>
       </c>
       <c r="L22" t="n">
         <v>1.79</v>
       </c>
       <c r="M22" t="n">
-        <v>1.91</v>
+        <v>9.48</v>
       </c>
       <c r="N22" t="n">
-        <v>3.38</v>
+        <v>8.26</v>
       </c>
       <c r="O22" t="n">
         <v>2.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45112.55208333334</v>
+        <v>45113.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="I23" t="n">
         <v>324.5355649770458</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.33</v>
+        <v>-8.67</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
         <v>0.67</v>
       </c>
       <c r="N23" t="n">
-        <v>1.67</v>
+        <v>6.91</v>
       </c>
       <c r="O23" t="n">
         <v>-8.26</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.48</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45149.38541666666</v>
+        <v>45149.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I24" t="n">
         <v>314.1054336787432</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.07</v>
+        <v>-3.68</v>
       </c>
       <c r="L24" t="n">
         <v>7.36</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.45</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45163.55208333334</v>
+        <v>45166.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="I25" t="n">
         <v>321.5304246394319</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.32</v>
+        <v>-2.55</v>
       </c>
       <c r="L25" t="n">
         <v>2.87</v>
@@ -1866,7 +2165,7 @@
         <v>0.95</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="O25" t="n">
         <v>-0.63</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.21</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45300.38541666666</v>
+        <v>45300.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="I26" t="n">
         <v>616.1540025041508</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>134</v>
+        <v>134.1666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>93.79000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.86</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>644</v>
+        <v>677</v>
       </c>
       <c r="I27" t="n">
         <v>646.9721892898893</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.55</v>
+        <v>-9.9</v>
       </c>
       <c r="L27" t="n">
-        <v>5.36</v>
+        <v>11.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.41</v>
       </c>
       <c r="N27" t="n">
-        <v>5.13</v>
+        <v>6.06</v>
       </c>
       <c r="O27" t="n">
         <v>-2.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>763</v>
+        <v>700</v>
       </c>
       <c r="I28" t="n">
         <v>716.4282019144476</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>12.7</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>4.73</v>
       </c>
       <c r="M28" t="n">
-        <v>-0</v>
+        <v>0.79</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>8.65</v>
       </c>
       <c r="O28" t="n">
         <v>6.06</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45350.55208333334</v>
+        <v>45351.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="I29" t="n">
         <v>745.419783276571</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.57</v>
+        <v>-6.71</v>
       </c>
       <c r="L29" t="n">
         <v>8.140000000000001</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.43</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45356.38541666666</v>
+        <v>45356.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I30" t="n">
         <v>719.4665953024304</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.08</v>
+        <v>-4.15</v>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>4.55</v>
       </c>
       <c r="M30" t="n">
         <v>0.13</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.79</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="I31" t="n">
         <v>690.297747813416</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>23</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>6.28</v>
+        <v>1.26</v>
       </c>
       <c r="L31" t="n">
         <v>1.68</v>
@@ -2208,7 +2579,7 @@
         <v>1.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>6.41</v>
       </c>
       <c r="O31" t="n">
         <v>-3.63</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.98</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45421.38541666666</v>
+        <v>45421.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="I32" t="n">
         <v>759.2832283235454</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>7.64</v>
+        <v>6.79</v>
       </c>
       <c r="L32" t="n">
         <v>6.36</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.97</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="I33" t="n">
         <v>745.6447103364853</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>2.12</v>
+        <v>-0.66</v>
       </c>
       <c r="L33" t="n">
         <v>7.95</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.04</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45482.55208333334</v>
+        <v>45483.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="I34" t="n">
         <v>747.3748228797499</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
-        <v>1.45</v>
+        <v>-2.11</v>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="M34" t="n">
         <v>0.38</v>
       </c>
       <c r="N34" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
         <v>2.98</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45491.38541666666</v>
+        <v>45491.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="I35" t="n">
         <v>803.2156612539628</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.05</v>
+        <v>-9.27</v>
       </c>
       <c r="L35" t="n">
-        <v>6.99</v>
+        <v>10.08</v>
       </c>
       <c r="M35" t="n">
         <v>0.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.79</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1278</v>
+        <v>1240</v>
       </c>
       <c r="I36" t="n">
         <v>1244.568408450809</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>116</v>
+        <v>116.8333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>57.2</v>
+        <v>52.52</v>
       </c>
       <c r="L36" t="n">
         <v>10.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.63</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1262</v>
+        <v>1298</v>
       </c>
       <c r="I37" t="n">
         <v>1277.844338534635</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.77</v>
+        <v>-4.68</v>
       </c>
       <c r="L37" t="n">
-        <v>3.95</v>
+        <v>5.16</v>
       </c>
       <c r="M37" t="n">
         <v>1.49</v>
       </c>
       <c r="N37" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="O37" t="n">
         <v>-4.69</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1333</v>
+        <v>1284</v>
       </c>
       <c r="I38" t="n">
         <v>1291.603097063642</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>2.7</v>
+        <v>-1.08</v>
       </c>
       <c r="L38" t="n">
         <v>3.08</v>
@@ -2607,7 +3062,7 @@
         <v>1.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
         <v>3.01</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1194</v>
+        <v>1219</v>
       </c>
       <c r="I39" t="n">
         <v>1202.86404217696</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>7.01</v>
+        <v>5.06</v>
       </c>
       <c r="L39" t="n">
         <v>4.36</v>
       </c>
       <c r="M39" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="N39" t="n">
         <v>4.74</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.29</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45677.55208333334</v>
+        <v>45678.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1198</v>
+        <v>1116</v>
       </c>
       <c r="I40" t="n">
         <v>1138.166114855291</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.72</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>2.63</v>
+        <v>13.04</v>
       </c>
       <c r="M40" t="n">
-        <v>-0</v>
+        <v>0.67</v>
       </c>
       <c r="N40" t="n">
-        <v>0.9</v>
+        <v>8.18</v>
       </c>
       <c r="O40" t="n">
         <v>2.09</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1180</v>
+        <v>1220</v>
       </c>
       <c r="I41" t="n">
         <v>1210.974947767396</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.73</v>
+        <v>-9.32</v>
       </c>
       <c r="L41" t="n">
-        <v>6.63</v>
+        <v>9.77</v>
       </c>
       <c r="M41" t="n">
         <v>1.43</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1156</v>
+        <v>1084</v>
       </c>
       <c r="I42" t="n">
         <v>1135.737614284386</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.25</v>
+        <v>-11.15</v>
       </c>
       <c r="L42" t="n">
-        <v>5.74</v>
+        <v>11.15</v>
       </c>
       <c r="M42" t="n">
         <v>0.17</v>
       </c>
       <c r="N42" t="n">
-        <v>3.67</v>
+        <v>4.93</v>
       </c>
       <c r="O42" t="n">
         <v>3.39</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.41</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45729.55208333334</v>
+        <v>45733.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>959</v>
+        <v>996</v>
       </c>
       <c r="I43" t="n">
         <v>984.0770220916709</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>11.53</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L43" t="n">
         <v>6.73</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.38541666666</v>
+        <v>45751.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="I44" t="n">
         <v>1018.515233431914</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>2.41</v>
+        <v>1.61</v>
       </c>
       <c r="L44" t="n">
         <v>3.51</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45754.55208333334</v>
+        <v>45755.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1003</v>
+        <v>1050</v>
       </c>
       <c r="I45" t="n">
         <v>1049.426702385261</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.89</v>
+        <v>-3.75</v>
       </c>
       <c r="L45" t="n">
-        <v>1.19</v>
+        <v>4.35</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O45" t="n">
         <v>-5.24</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11.52</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1195</v>
+        <v>1125</v>
       </c>
       <c r="I46" t="n">
         <v>1174.35211541708</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>13.81</v>
+        <v>7.14</v>
       </c>
       <c r="L46" t="n">
         <v>3.43</v>
       </c>
       <c r="M46" t="n">
-        <v>0.58</v>
+        <v>2.59</v>
       </c>
       <c r="N46" t="n">
-        <v>4.62</v>
+        <v>4.85</v>
       </c>
       <c r="O46" t="n">
         <v>3.89</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45791.38541666666</v>
+        <v>45791.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="I47" t="n">
         <v>1238.281023277687</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.04</v>
+        <v>-10.49</v>
       </c>
       <c r="L47" t="n">
-        <v>10.31</v>
+        <v>10.76</v>
       </c>
       <c r="M47" t="n">
         <v>4.22</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.83</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1752</v>
+        <v>1699</v>
       </c>
       <c r="I48" t="n">
         <v>1708.750246468754</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>40.95</v>
+        <v>36.69</v>
       </c>
       <c r="L48" t="n">
         <v>1.13</v>
@@ -3177,7 +3752,7 @@
         <v>1.73</v>
       </c>
       <c r="N48" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>4.54</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.39</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1587</v>
+        <v>1640</v>
       </c>
       <c r="I49" t="n">
         <v>1609.908648313404</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>6.59</v>
+        <v>3.47</v>
       </c>
       <c r="L49" t="n">
         <v>3.88</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1600</v>
+        <v>1536</v>
       </c>
       <c r="I50" t="n">
         <v>1573.399910845155</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.44</v>
+        <v>-6.34</v>
       </c>
       <c r="L50" t="n">
-        <v>3.78</v>
+        <v>6.34</v>
       </c>
       <c r="M50" t="n">
         <v>-0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>2.96</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45916.55208333334</v>
+        <v>45917.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1534</v>
+        <v>1592</v>
       </c>
       <c r="I51" t="n">
         <v>1568.506210940179</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K51" t="n">
-        <v>0.13</v>
+        <v>-3.65</v>
       </c>
       <c r="L51" t="n">
-        <v>4.17</v>
+        <v>4.62</v>
       </c>
       <c r="M51" t="n">
         <v>0.92</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.85</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46001.38541666666</v>
+        <v>46001.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>2019</v>
+        <v>1956</v>
       </c>
       <c r="I52" t="n">
         <v>1981.570601164676</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>26.82</v>
+        <v>22.86</v>
       </c>
       <c r="L52" t="n">
         <v>3.45</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2058</v>
+        <v>2157</v>
       </c>
       <c r="I53" t="n">
         <v>2109.978131443018</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.21</v>
+        <v>-10.28</v>
       </c>
       <c r="L53" t="n">
-        <v>5.98</v>
+        <v>10.58</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="N53" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="O53" t="n">
         <v>-5.46</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.57</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46043.55208333334</v>
+        <v>46044.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2336</v>
+        <v>2297</v>
       </c>
       <c r="I54" t="n">
         <v>2302.649599407612</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>8.300000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="L54" t="n">
         <v>4.36</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>10.75</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2440</v>
+        <v>2594</v>
       </c>
       <c r="I55" t="n">
         <v>2482.152643434349</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.23</v>
+        <v>-12.93</v>
       </c>
       <c r="L55" t="n">
-        <v>6.49</v>
+        <v>13.41</v>
       </c>
       <c r="M55" t="n">
         <v>3.79</v>
       </c>
       <c r="N55" t="n">
-        <v>6.18</v>
+        <v>6.64</v>
       </c>
       <c r="O55" t="n">
         <v>-0.64</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>11.62</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2515</v>
+        <v>2277.9</v>
       </c>
       <c r="I56" t="n">
         <v>2471.029730520606</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.05</v>
+        <v>-12.19</v>
       </c>
       <c r="L56" t="n">
-        <v>5.2</v>
+        <v>20.26</v>
       </c>
       <c r="M56" t="n">
-        <v>0.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>6.99</v>
+        <v>11.53</v>
       </c>
       <c r="O56" t="n">
         <v>6.64</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>12.19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46083.38541666666</v>
+        <v>46083.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>2474</v>
+        <v>2505.9</v>
       </c>
       <c r="I57" t="n">
         <v>2498.624034977832</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.609999999999999</v>
+        <v>-10.01</v>
       </c>
       <c r="L57" t="n">
         <v>12.25</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46100.55208333334</v>
+        <v>46101.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2530.3</v>
+        <v>2414.9</v>
       </c>
       <c r="I58" t="n">
         <v>2491.391818374987</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>0.97</v>
+        <v>-3.63</v>
       </c>
       <c r="L58" t="n">
-        <v>2.93</v>
+        <v>3.81</v>
       </c>
       <c r="M58" t="n">
         <v>2.44</v>
       </c>
       <c r="N58" t="n">
-        <v>3.02</v>
+        <v>4.75</v>
       </c>
       <c r="O58" t="n">
         <v>2.41</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2437.2</v>
+        <v>2532.8</v>
       </c>
       <c r="I59" t="n">
         <v>2520.492912028792</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.92</v>
+        <v>-4.88</v>
       </c>
       <c r="L59" t="n">
         <v>5.96</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.64</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3312</v>
+        <v>3210.4</v>
       </c>
       <c r="I60" t="n">
         <v>3243.612117648282</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K60" t="n">
-        <v>30.76</v>
+        <v>26.75</v>
       </c>
       <c r="L60" t="n">
         <v>4.36</v>
@@ -3861,7 +4580,7 @@
         <v>0.88</v>
       </c>
       <c r="N60" t="n">
-        <v>3.72</v>
+        <v>4.74</v>
       </c>
       <c r="O60" t="n">
         <v>4.22</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.99</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2842</v>
+        <v>2989.2</v>
       </c>
       <c r="I61" t="n">
         <v>2962.970223178939</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>11.48</v>
+        <v>6.89</v>
       </c>
       <c r="L61" t="n">
         <v>3.5</v>
@@ -3918,7 +4649,7 @@
         <v>1.89</v>
       </c>
       <c r="N61" t="n">
-        <v>2.61</v>
+        <v>4.25</v>
       </c>
       <c r="O61" t="n">
         <v>-4.74</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>8.91</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2804.1</v>
+        <v>2750.3</v>
       </c>
       <c r="I62" t="n">
         <v>2779.735686246942</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.19</v>
+        <v>-7.99</v>
       </c>
       <c r="L62" t="n">
-        <v>6.33</v>
+        <v>8.44</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>0.15</v>
       </c>
       <c r="N62" t="n">
         <v>4.02</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2782</v>
+        <v>2870.4</v>
       </c>
       <c r="I63" t="n">
         <v>2845.178819673715</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.15</v>
+        <v>-4.37</v>
       </c>
       <c r="L63" t="n">
-        <v>3.23</v>
+        <v>5.04</v>
       </c>
       <c r="M63" t="n">
         <v>0.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>2718</v>
+        <v>2715.6</v>
       </c>
       <c r="I64" t="n">
         <v>2717.605435338861</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.31</v>
+        <v>-5.39</v>
       </c>
       <c r="L64" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="M64" t="n">
         <v>0.77</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.26</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2639</v>
+        <v>2779.9</v>
       </c>
       <c r="I65" t="n">
         <v>2753.163521055689</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>2.82</v>
+        <v>-2.37</v>
       </c>
       <c r="L65" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="M65" t="n">
         <v>0.85</v>
       </c>
       <c r="N65" t="n">
-        <v>1.35</v>
+        <v>5.19</v>
       </c>
       <c r="O65" t="n">
         <v>-0.18</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.83</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46296.38541666666</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>3246.9</v>
+        <v>3202.3</v>
       </c>
       <c r="I66" t="n">
         <v>3227.470501948717</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K66" t="n">
-        <v>16.8</v>
+        <v>15.19</v>
       </c>
       <c r="L66" t="n">
         <v>6.36</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>33</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.4</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="11">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.46</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.789999999999999</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.79000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.51</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.95</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.25</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.66</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.89</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.23</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
